--- a/dae_il/task_list_dae_il.xlsx
+++ b/dae_il/task_list_dae_il.xlsx
@@ -8,19 +8,20 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\lbh00\OneDrive\문서\감사\감사자료\audit-automation\dae_il\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4490DB68-A595-4A11-A33B-8EECE2D9ED73}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{569FD236-3996-45AB-B20D-CDEA101801F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="16220" firstSheet="4" activeTab="7" xr2:uid="{0988228D-CB65-49FF-A818-8D2DE82566F6}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="16220" firstSheet="1" activeTab="3" xr2:uid="{0988228D-CB65-49FF-A818-8D2DE82566F6}"/>
   </bookViews>
   <sheets>
     <sheet name="settings" sheetId="1" r:id="rId1"/>
     <sheet name="host1_총계정원장" sheetId="2" r:id="rId2"/>
     <sheet name="host1_상세검색_시나리오" sheetId="3" r:id="rId3"/>
-    <sheet name="host1_벤포드법칙분석" sheetId="5" r:id="rId4"/>
-    <sheet name="host1_전기 데이터 비교 분석" sheetId="8" r:id="rId5"/>
-    <sheet name="host1_이중거래처분석" sheetId="6" r:id="rId6"/>
-    <sheet name="host1_외상매출매입상계" sheetId="7" r:id="rId7"/>
-    <sheet name="host2_분개장AI분석" sheetId="4" r:id="rId8"/>
+    <sheet name="host1_이자비용적정성test" sheetId="9" r:id="rId4"/>
+    <sheet name="host1_벤포드법칙분석" sheetId="5" r:id="rId5"/>
+    <sheet name="host1_전기 데이터 비교 분석" sheetId="8" r:id="rId6"/>
+    <sheet name="host1_이중거래처분석" sheetId="6" r:id="rId7"/>
+    <sheet name="host1_외상매출매입상계" sheetId="7" r:id="rId8"/>
+    <sheet name="host2_분개장AI분석" sheetId="4" r:id="rId9"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -43,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="60">
   <si>
     <t>항목</t>
   </si>
@@ -255,6 +256,16 @@
   <si>
     <t>유동성장기부채</t>
     <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>이자비용적정성</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>하나 장기운전자금4(29320)</t>
+  </si>
+  <si>
+    <t>하나/장기운전자금-34142 / 하나 장기운전자금-34142</t>
   </si>
 </sst>
 </file>
@@ -1056,6 +1067,78 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{50FFCEB5-88FF-45C9-9834-22A548B0A896}">
+  <dimension ref="A1:D4"/>
+  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="1" max="1" width="14.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="63.83203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.33203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A2" t="s">
+        <v>57</v>
+      </c>
+      <c r="B2" t="s">
+        <v>58</v>
+      </c>
+      <c r="C2" t="s">
+        <v>35</v>
+      </c>
+      <c r="D2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A3" t="s">
+        <v>57</v>
+      </c>
+      <c r="B3" t="s">
+        <v>59</v>
+      </c>
+      <c r="C3" t="s">
+        <v>35</v>
+      </c>
+      <c r="D3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A4" t="s">
+        <v>57</v>
+      </c>
+      <c r="B4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C4" t="s">
+        <v>28</v>
+      </c>
+      <c r="D4" t="s">
+        <v>30</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9CE977AC-918C-48AD-A858-7636F2EFDC97}">
   <dimension ref="A1:B6"/>
   <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
@@ -1118,7 +1201,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{265A6539-2564-46BF-942B-EEC385B53B6D}">
   <dimension ref="A1:B3"/>
   <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
@@ -1157,7 +1240,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{04D14481-7FF3-4693-99E5-2CB88F450E06}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
@@ -1167,7 +1250,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F26966BA-9AA6-46A4-A0FC-D608B070C3C3}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
@@ -1177,7 +1260,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0E4E540D-2F54-444B-8CC0-15566B81F298}">
   <dimension ref="A1:D10"/>
   <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
